--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,804 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123286106</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Enstensviken, Enstensviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>629246</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6891517</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123286328</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105456</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Enstensviken, Enstensviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>629246</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6891517</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123285641</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Enstensviken, Enstensviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629242</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6891557</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123286037</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Enstensviken, Enstensviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>629190</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6891571</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123285493</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90917</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Enstensviken, Enstensviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>629242</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6891557</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123285195</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Enstensviken, Enstensviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>629249</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6891580</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123285762</v>
+      </c>
+      <c r="B10" t="n">
+        <v>94778</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Enstensviken, Enstensviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>629242</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6891557</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286106</v>
+        <v>123286328</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>105456</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,7 +955,7 @@
         <v>6891517</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286328</v>
+        <v>123285195</v>
       </c>
       <c r="B5" t="n">
-        <v>105456</v>
+        <v>95911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629246</v>
+        <v>629249</v>
       </c>
       <c r="R5" t="n">
-        <v>6891517</v>
+        <v>6891580</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285641</v>
+        <v>123286037</v>
       </c>
       <c r="B6" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,38 +1145,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629242</v>
+        <v>629190</v>
       </c>
       <c r="R6" t="n">
-        <v>6891557</v>
+        <v>6891571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286037</v>
+        <v>123285762</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>94778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,50 +1266,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629190</v>
+        <v>629242</v>
       </c>
       <c r="R7" t="n">
-        <v>6891571</v>
+        <v>6891557</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285493</v>
+        <v>123285641</v>
       </c>
       <c r="B8" t="n">
-        <v>90917</v>
+        <v>95911</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,25 +1378,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,7 +1412,7 @@
         <v>6891557</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285195</v>
+        <v>123285493</v>
       </c>
       <c r="B9" t="n">
-        <v>95911</v>
+        <v>90917</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,25 +1495,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629249</v>
+        <v>629242</v>
       </c>
       <c r="R9" t="n">
-        <v>6891580</v>
+        <v>6891557</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123285762</v>
+        <v>123286106</v>
       </c>
       <c r="B10" t="n">
-        <v>94778</v>
+        <v>90952</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R10" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286328</v>
+        <v>123285641</v>
       </c>
       <c r="B4" t="n">
-        <v>105456</v>
+        <v>95914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R4" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123285195</v>
+        <v>123286328</v>
       </c>
       <c r="B5" t="n">
-        <v>95911</v>
+        <v>105459</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629249</v>
+        <v>629246</v>
       </c>
       <c r="R5" t="n">
-        <v>6891580</v>
+        <v>6891517</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286037</v>
+        <v>123285493</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>90920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,50 +1150,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629190</v>
+        <v>629242</v>
       </c>
       <c r="R6" t="n">
-        <v>6891571</v>
+        <v>6891557</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123285762</v>
+        <v>123286106</v>
       </c>
       <c r="B7" t="n">
-        <v>94778</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R7" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285641</v>
+        <v>123286037</v>
       </c>
       <c r="B8" t="n">
-        <v>95911</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,38 +1374,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629242</v>
+        <v>629190</v>
       </c>
       <c r="R8" t="n">
-        <v>6891557</v>
+        <v>6891571</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285493</v>
+        <v>123285762</v>
       </c>
       <c r="B9" t="n">
-        <v>90917</v>
+        <v>94781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286106</v>
+        <v>123285195</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
+        <v>95914</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629246</v>
+        <v>629249</v>
       </c>
       <c r="R10" t="n">
-        <v>6891517</v>
+        <v>6891580</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123285641</v>
+        <v>123285195</v>
       </c>
       <c r="B4" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629242</v>
+        <v>629249</v>
       </c>
       <c r="R4" t="n">
-        <v>6891557</v>
+        <v>6891580</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286328</v>
+        <v>123286037</v>
       </c>
       <c r="B5" t="n">
-        <v>105459</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1033,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629246</v>
+        <v>629190</v>
       </c>
       <c r="R5" t="n">
-        <v>6891517</v>
+        <v>6891571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285493</v>
+        <v>123286106</v>
       </c>
       <c r="B6" t="n">
-        <v>90920</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,25 +1154,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R6" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286106</v>
+        <v>123285493</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>90922</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1266,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R7" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123286037</v>
+        <v>123286328</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>105461</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,47 +1378,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629190</v>
+        <v>629246</v>
       </c>
       <c r="R8" t="n">
-        <v>6891571</v>
+        <v>6891517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285762</v>
+        <v>123285641</v>
       </c>
       <c r="B9" t="n">
-        <v>94781</v>
+        <v>95916</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2813</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,7 +1524,7 @@
         <v>6891557</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1563,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123285195</v>
+        <v>123285762</v>
       </c>
       <c r="B10" t="n">
-        <v>95914</v>
+        <v>94783</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629249</v>
+        <v>629242</v>
       </c>
       <c r="R10" t="n">
-        <v>6891580</v>
+        <v>6891557</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123285195</v>
+        <v>123286037</v>
       </c>
       <c r="B4" t="n">
-        <v>95916</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +921,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629249</v>
+        <v>629190</v>
       </c>
       <c r="R4" t="n">
-        <v>6891580</v>
+        <v>6891571</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286037</v>
+        <v>123285195</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>95916</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,50 +1042,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629190</v>
+        <v>629249</v>
       </c>
       <c r="R5" t="n">
-        <v>6891571</v>
+        <v>6891580</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286037</v>
+        <v>123286328</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>105467</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,47 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629190</v>
+        <v>629246</v>
       </c>
       <c r="R4" t="n">
-        <v>6891571</v>
+        <v>6891517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123285195</v>
+        <v>123286037</v>
       </c>
       <c r="B5" t="n">
-        <v>95916</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,41 +1033,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629249</v>
+        <v>629190</v>
       </c>
       <c r="R5" t="n">
-        <v>6891580</v>
+        <v>6891571</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286106</v>
+        <v>123285493</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>90928</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,25 +1154,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R6" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123285493</v>
+        <v>123286106</v>
       </c>
       <c r="B7" t="n">
-        <v>90922</v>
+        <v>90963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1266,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R7" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123286328</v>
+        <v>123285762</v>
       </c>
       <c r="B8" t="n">
-        <v>105461</v>
+        <v>94789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>2813</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,13 +1406,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R8" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,7 +1481,7 @@
         <v>123285641</v>
       </c>
       <c r="B9" t="n">
-        <v>95916</v>
+        <v>95922</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123285762</v>
+        <v>123285195</v>
       </c>
       <c r="B10" t="n">
-        <v>94783</v>
+        <v>95922</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629242</v>
+        <v>629249</v>
       </c>
       <c r="R10" t="n">
-        <v>6891557</v>
+        <v>6891580</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286328</v>
+        <v>123286037</v>
       </c>
       <c r="B4" t="n">
-        <v>105467</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,38 +921,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629246</v>
+        <v>629190</v>
       </c>
       <c r="R4" t="n">
-        <v>6891517</v>
+        <v>6891571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286037</v>
+        <v>123285641</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>95925</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,47 +1042,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629190</v>
+        <v>629242</v>
       </c>
       <c r="R5" t="n">
-        <v>6891571</v>
+        <v>6891557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285493</v>
+        <v>123285762</v>
       </c>
       <c r="B6" t="n">
-        <v>90928</v>
+        <v>94792</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2813</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286106</v>
+        <v>123286328</v>
       </c>
       <c r="B7" t="n">
-        <v>90963</v>
+        <v>105470</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1271,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,7 +1305,7 @@
         <v>6891517</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285762</v>
+        <v>123285195</v>
       </c>
       <c r="B8" t="n">
-        <v>94789</v>
+        <v>95925</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629242</v>
+        <v>629249</v>
       </c>
       <c r="R8" t="n">
-        <v>6891557</v>
+        <v>6891580</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285641</v>
+        <v>123285493</v>
       </c>
       <c r="B9" t="n">
-        <v>95922</v>
+        <v>90931</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1495,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,7 +1529,7 @@
         <v>6891557</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123285195</v>
+        <v>123286106</v>
       </c>
       <c r="B10" t="n">
-        <v>95922</v>
+        <v>90966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629249</v>
+        <v>629246</v>
       </c>
       <c r="R10" t="n">
-        <v>6891580</v>
+        <v>6891517</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286037</v>
+        <v>123285195</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>95942</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,50 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629190</v>
+        <v>629249</v>
       </c>
       <c r="R4" t="n">
-        <v>6891571</v>
+        <v>6891580</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123285641</v>
+        <v>123285493</v>
       </c>
       <c r="B5" t="n">
-        <v>95925</v>
+        <v>90948</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,7 +1067,7 @@
         <v>6891557</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285762</v>
+        <v>123286037</v>
       </c>
       <c r="B6" t="n">
-        <v>94792</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,41 +1145,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629242</v>
+        <v>629190</v>
       </c>
       <c r="R6" t="n">
-        <v>6891557</v>
+        <v>6891571</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1257,7 @@
         <v>123286328</v>
       </c>
       <c r="B7" t="n">
-        <v>105470</v>
+        <v>105487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1371,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285195</v>
+        <v>123285641</v>
       </c>
       <c r="B8" t="n">
-        <v>95925</v>
+        <v>95942</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,13 +1406,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629249</v>
+        <v>629242</v>
       </c>
       <c r="R8" t="n">
-        <v>6891580</v>
+        <v>6891557</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285493</v>
+        <v>123286106</v>
       </c>
       <c r="B9" t="n">
-        <v>90931</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,25 +1495,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R9" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286106</v>
+        <v>123285762</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>94809</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R10" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>123285195</v>
       </c>
       <c r="B4" t="n">
-        <v>95942</v>
+        <v>95949</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123285493</v>
+        <v>123285641</v>
       </c>
       <c r="B5" t="n">
-        <v>90948</v>
+        <v>95949</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
         <v>6891557</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286037</v>
+        <v>123285493</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>90953</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,50 +1150,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629190</v>
+        <v>629242</v>
       </c>
       <c r="R6" t="n">
-        <v>6891571</v>
+        <v>6891557</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286328</v>
+        <v>123286106</v>
       </c>
       <c r="B7" t="n">
-        <v>105487</v>
+        <v>90988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,7 +1296,7 @@
         <v>6891517</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285641</v>
+        <v>123286328</v>
       </c>
       <c r="B8" t="n">
-        <v>95942</v>
+        <v>105503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R8" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123286106</v>
+        <v>123285762</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>94815</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R9" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123285762</v>
+        <v>123286037</v>
       </c>
       <c r="B10" t="n">
-        <v>94809</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,41 +1598,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629242</v>
+        <v>629190</v>
       </c>
       <c r="R10" t="n">
-        <v>6891557</v>
+        <v>6891571</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123285195</v>
+        <v>123285641</v>
       </c>
       <c r="B4" t="n">
-        <v>95949</v>
+        <v>95951</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629249</v>
+        <v>629242</v>
       </c>
       <c r="R4" t="n">
-        <v>6891580</v>
+        <v>6891557</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123285641</v>
+        <v>123286037</v>
       </c>
       <c r="B5" t="n">
-        <v>95949</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1038,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629242</v>
+        <v>629190</v>
       </c>
       <c r="R5" t="n">
-        <v>6891557</v>
+        <v>6891571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285493</v>
+        <v>123285195</v>
       </c>
       <c r="B6" t="n">
-        <v>90953</v>
+        <v>95951</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,25 +1159,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629242</v>
+        <v>629249</v>
       </c>
       <c r="R6" t="n">
-        <v>6891557</v>
+        <v>6891580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1262,7 @@
         <v>123286106</v>
       </c>
       <c r="B7" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123286328</v>
+        <v>123285762</v>
       </c>
       <c r="B8" t="n">
-        <v>105503</v>
+        <v>94817</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>2813</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R8" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285762</v>
+        <v>123285493</v>
       </c>
       <c r="B9" t="n">
-        <v>94815</v>
+        <v>90955</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2813</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286037</v>
+        <v>123286328</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>105505</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,47 +1607,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629190</v>
+        <v>629246</v>
       </c>
       <c r="R10" t="n">
-        <v>6891571</v>
+        <v>6891517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285493</v>
+        <v>123286328</v>
       </c>
       <c r="B9" t="n">
-        <v>90955</v>
+        <v>105505</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R9" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286328</v>
+        <v>123285493</v>
       </c>
       <c r="B10" t="n">
-        <v>105505</v>
+        <v>90955</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R10" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123285641</v>
+        <v>123286328</v>
       </c>
       <c r="B4" t="n">
-        <v>95951</v>
+        <v>105080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R4" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286037</v>
+        <v>123285195</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>96332</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,50 +1033,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629190</v>
+        <v>629249</v>
       </c>
       <c r="R5" t="n">
-        <v>6891571</v>
+        <v>6891580</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285195</v>
+        <v>123286037</v>
       </c>
       <c r="B6" t="n">
-        <v>95951</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,41 +1145,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629249</v>
+        <v>629190</v>
       </c>
       <c r="R6" t="n">
-        <v>6891580</v>
+        <v>6891571</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286106</v>
+        <v>123285762</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>95325</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,25 +1266,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R7" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285762</v>
+        <v>123286106</v>
       </c>
       <c r="B8" t="n">
-        <v>94817</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,25 +1378,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R8" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123286328</v>
+        <v>123285641</v>
       </c>
       <c r="B9" t="n">
-        <v>105505</v>
+        <v>96332</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R9" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1563,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123285762</v>
+        <v>123285641</v>
       </c>
       <c r="B7" t="n">
-        <v>95325</v>
+        <v>96332</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1266,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2813</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
         <v>6891557</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123286106</v>
+        <v>123285762</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>95325</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R8" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123285641</v>
+        <v>123286106</v>
       </c>
       <c r="B9" t="n">
-        <v>96332</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,13 +1523,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R9" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286328</v>
+        <v>123285195</v>
       </c>
       <c r="B4" t="n">
-        <v>105080</v>
+        <v>96332</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629246</v>
+        <v>629249</v>
       </c>
       <c r="R4" t="n">
-        <v>6891517</v>
+        <v>6891580</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123285195</v>
+        <v>123286328</v>
       </c>
       <c r="B5" t="n">
-        <v>96332</v>
+        <v>105080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629249</v>
+        <v>629246</v>
       </c>
       <c r="R5" t="n">
-        <v>6891580</v>
+        <v>6891517</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286037</v>
+        <v>123285493</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,50 +1145,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629190</v>
+        <v>629242</v>
       </c>
       <c r="R6" t="n">
-        <v>6891571</v>
+        <v>6891557</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123285641</v>
+        <v>123285762</v>
       </c>
       <c r="B7" t="n">
-        <v>96332</v>
+        <v>95325</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>2813</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,7 +1291,7 @@
         <v>6891557</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285762</v>
+        <v>123285641</v>
       </c>
       <c r="B8" t="n">
-        <v>95325</v>
+        <v>96332</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,7 +1403,7 @@
         <v>6891557</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123285493</v>
+        <v>123286037</v>
       </c>
       <c r="B10" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,41 +1598,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629242</v>
+        <v>629190</v>
       </c>
       <c r="R10" t="n">
-        <v>6891557</v>
+        <v>6891571</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 6178-2025 artfynd.xlsx
+++ b/artfynd/A 6178-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123285195</v>
+        <v>123285641</v>
       </c>
       <c r="B4" t="n">
         <v>96332</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629249</v>
+        <v>629242</v>
       </c>
       <c r="R4" t="n">
-        <v>6891580</v>
+        <v>6891557</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Välspridd på många lågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286328</v>
+        <v>123285493</v>
       </c>
       <c r="B5" t="n">
-        <v>105080</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629246</v>
+        <v>629242</v>
       </c>
       <c r="R5" t="n">
-        <v>6891517</v>
+        <v>6891557</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123285493</v>
+        <v>123285195</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>96332</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629242</v>
+        <v>629249</v>
       </c>
       <c r="R6" t="n">
-        <v>6891557</v>
+        <v>6891580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123285641</v>
+        <v>123286328</v>
       </c>
       <c r="B8" t="n">
-        <v>96332</v>
+        <v>105080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629242</v>
+        <v>629246</v>
       </c>
       <c r="R8" t="n">
-        <v>6891557</v>
+        <v>6891517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Välspridd på många lågor</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123286106</v>
+        <v>123286037</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,41 +1486,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629246</v>
+        <v>629190</v>
       </c>
       <c r="R9" t="n">
-        <v>6891517</v>
+        <v>6891571</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286037</v>
+        <v>123286106</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,50 +1607,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Enstensviken, Enstensviken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629190</v>
+        <v>629246</v>
       </c>
       <c r="R10" t="n">
-        <v>6891571</v>
+        <v>6891517</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
